--- a/doc/开发工作计划.xlsx
+++ b/doc/开发工作计划.xlsx
@@ -82,7 +82,7 @@
     <t>Phase 2: HAL 接口定义</t>
   </si>
   <si>
-    <t>5个纯虚接口+工厂注册</t>
+    <t>纯虚接口+工厂注册</t>
   </si>
   <si>
     <t>Phase 3: 硬件 HAL 实现</t>
